--- a/backend/src/main/resources/templates/alltemple_template-zhiyi.xlsx
+++ b/backend/src/main/resources/templates/alltemple_template-zhiyi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="报关单" sheetId="1" r:id="rId1"/>
@@ -1486,7 +1486,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1786,6 +1786,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2539,7 +2543,7 @@
       <c r="P6" s="82"/>
       <c r="Q6" s="84"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:20">
+    <row r="7" ht="28" customHeight="1" spans="1:20">
       <c r="A7" s="101" t="s">
         <v>18</v>
       </c>
@@ -2744,10 +2748,10 @@
       </c>
       <c r="N13" s="80"/>
       <c r="O13" s="99"/>
-      <c r="P13" s="98" t="s">
+      <c r="P13" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="99"/>
+      <c r="Q13" s="112"/>
     </row>
     <row r="14" s="73" customFormat="1" ht="15" customHeight="1" spans="1:20">
       <c r="A14" s="87" t="s">
@@ -2772,7 +2776,7 @@
       <c r="T14" s="76"/>
     </row>
     <row r="15" s="74" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="113" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="80"/>
@@ -2781,7 +2785,7 @@
       <c r="E15" s="80"/>
       <c r="F15" s="80"/>
       <c r="G15" s="80"/>
-      <c r="H15" s="112" t="s">
+      <c r="H15" s="114" t="s">
         <v>53</v>
       </c>
       <c r="I15" s="80"/>
@@ -2799,22 +2803,22 @@
       <c r="A16" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="113"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="113"/>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="115"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="115"/>
+      <c r="Q16" s="117"/>
       <c r="T16" s="76"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:20">
@@ -2839,257 +2843,257 @@
       <c r="Q17" s="99"/>
     </row>
     <row r="18" s="75" customFormat="1" ht="18.75" customHeight="1" spans="1:20">
-      <c r="A18" s="116" t="s">
+      <c r="A18" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="117" t="s">
+      <c r="B18" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="117" t="s">
+      <c r="C18" s="120"/>
+      <c r="D18" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="117" t="s">
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="117" t="s">
+      <c r="H18" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="117" t="s">
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="119" t="s">
         <v>61</v>
       </c>
-      <c r="L18" s="117" t="s">
+      <c r="L18" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="M18" s="118"/>
-      <c r="N18" s="117" t="s">
+      <c r="M18" s="120"/>
+      <c r="N18" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="119" t="s">
+      <c r="O18" s="120"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="121" t="s">
         <v>64</v>
       </c>
       <c r="T18" s="76"/>
     </row>
     <row r="19" s="76" customFormat="1" spans="1:20">
-      <c r="A19" s="120" t="s">
+      <c r="A19" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="121" t="s">
+      <c r="B19" s="123" t="s">
         <v>66</v>
       </c>
       <c r="C19" s="82"/>
-      <c r="D19" s="121" t="s">
+      <c r="D19" s="123" t="s">
         <v>67</v>
       </c>
       <c r="E19" s="82"/>
       <c r="F19" s="82"/>
-      <c r="G19" s="121" t="s">
+      <c r="G19" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="122" t="s">
+      <c r="H19" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="123" t="s">
+      <c r="I19" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="124" t="s">
+      <c r="J19" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="125" t="s">
+      <c r="K19" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="121" t="s">
+      <c r="L19" s="123" t="s">
         <v>73</v>
       </c>
       <c r="M19" s="82"/>
-      <c r="N19" s="121" t="s">
+      <c r="N19" s="123" t="s">
         <v>74</v>
       </c>
       <c r="O19" s="82"/>
       <c r="P19" s="82"/>
-      <c r="Q19" s="126" t="s">
+      <c r="Q19" s="128" t="s">
         <v>75</v>
       </c>
-      <c r="R19" s="127"/>
+      <c r="R19" s="129"/>
     </row>
     <row r="20" s="76" customFormat="1" spans="1:20">
-      <c r="A20" s="128"/>
-      <c r="B20" s="129"/>
-      <c r="C20" s="129"/>
-      <c r="D20" s="130" t="s">
+      <c r="A20" s="130"/>
+      <c r="B20" s="131"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="131" t="s">
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="133"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="129"/>
-      <c r="O20" s="129"/>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="135"/>
-      <c r="R20" s="127"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="129"/>
     </row>
     <row r="21" s="76" customFormat="1" ht="39" customHeight="1" spans="1:20">
-      <c r="A21" s="128"/>
-      <c r="B21" s="129"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="136"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="129"/>
-      <c r="N21" s="129"/>
-      <c r="Q21" s="135"/>
-      <c r="R21" s="127"/>
+      <c r="A21" s="130"/>
+      <c r="B21" s="131"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="138"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="Q21" s="137"/>
+      <c r="R21" s="129"/>
     </row>
     <row r="22" s="76" customFormat="1" spans="1:20">
-      <c r="A22" s="120"/>
-      <c r="B22" s="121"/>
+      <c r="A22" s="122"/>
+      <c r="B22" s="123"/>
       <c r="C22" s="82"/>
-      <c r="D22" s="121"/>
+      <c r="D22" s="123"/>
       <c r="E22" s="82"/>
       <c r="F22" s="82"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="139"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="121"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="141"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="123"/>
       <c r="M22" s="82"/>
-      <c r="N22" s="121"/>
+      <c r="N22" s="123"/>
       <c r="O22" s="82"/>
       <c r="P22" s="82"/>
-      <c r="Q22" s="126"/>
-      <c r="R22" s="127"/>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="129"/>
     </row>
     <row r="23" s="76" customFormat="1" spans="1:20">
-      <c r="A23" s="128"/>
-      <c r="B23" s="129"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
-      <c r="Q23" s="135"/>
-      <c r="R23" s="127"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="131"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="135"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="131"/>
+      <c r="N23" s="131"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="131"/>
+      <c r="Q23" s="137"/>
+      <c r="R23" s="129"/>
     </row>
     <row r="24" s="76" customFormat="1" ht="40" customHeight="1" spans="1:20">
-      <c r="A24" s="128"/>
-      <c r="B24" s="129"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="136"/>
-      <c r="K24" s="137"/>
-      <c r="L24" s="129"/>
-      <c r="N24" s="129"/>
-      <c r="Q24" s="135"/>
-      <c r="R24" s="127"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="131"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="138"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="Q24" s="137"/>
+      <c r="R24" s="129"/>
     </row>
     <row r="25" s="76" customFormat="1" spans="1:20">
-      <c r="A25" s="120"/>
-      <c r="B25" s="121"/>
+      <c r="A25" s="122"/>
+      <c r="B25" s="123"/>
       <c r="C25" s="82"/>
-      <c r="D25" s="121"/>
+      <c r="D25" s="123"/>
       <c r="E25" s="82"/>
       <c r="F25" s="82"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="121"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="123"/>
       <c r="M25" s="82"/>
-      <c r="N25" s="121"/>
+      <c r="N25" s="123"/>
       <c r="O25" s="82"/>
       <c r="P25" s="82"/>
-      <c r="Q25" s="126"/>
-      <c r="R25" s="127"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="129"/>
     </row>
     <row r="26" s="76" customFormat="1" spans="1:20">
-      <c r="A26" s="128"/>
-      <c r="B26" s="129"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="133"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="129"/>
-      <c r="P26" s="129"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="127"/>
+      <c r="A26" s="130"/>
+      <c r="B26" s="131"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="134"/>
+      <c r="I26" s="134"/>
+      <c r="J26" s="135"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="131"/>
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="131"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="129"/>
     </row>
     <row r="27" s="76" customFormat="1" ht="42" customHeight="1" spans="1:20">
-      <c r="A27" s="128"/>
-      <c r="B27" s="129"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="136"/>
-      <c r="K27" s="137"/>
-      <c r="L27" s="129"/>
-      <c r="N27" s="129"/>
-      <c r="Q27" s="135"/>
-      <c r="R27" s="127"/>
+      <c r="A27" s="130"/>
+      <c r="B27" s="131"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="138"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="131"/>
+      <c r="N27" s="131"/>
+      <c r="Q27" s="137"/>
+      <c r="R27" s="129"/>
     </row>
     <row r="28" s="73" customFormat="1" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A28" s="141"/>
-      <c r="B28" s="142"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="143" t="s">
+      <c r="A28" s="143"/>
+      <c r="B28" s="144"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="142" t="s">
+      <c r="E28" s="144"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="142"/>
-      <c r="I28" s="142"/>
-      <c r="J28" s="143" t="s">
+      <c r="H28" s="144"/>
+      <c r="I28" s="144"/>
+      <c r="J28" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="142"/>
-      <c r="N28" s="142"/>
-      <c r="O28" s="143" t="s">
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="144"/>
+      <c r="N28" s="144"/>
+      <c r="O28" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="144"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="146"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:20">
       <c r="A29" s="81" t="s">
@@ -3130,25 +3134,25 @@
       <c r="K30" s="89"/>
       <c r="L30" s="89"/>
       <c r="M30" s="98"/>
-      <c r="Q30" s="145"/>
+      <c r="Q30" s="147"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:20">
-      <c r="A31" s="146" t="s">
+      <c r="A31" s="148" t="s">
         <v>85</v>
       </c>
       <c r="B31" s="80"/>
-      <c r="C31" s="147"/>
+      <c r="C31" s="149"/>
       <c r="D31" s="80"/>
       <c r="E31" s="80"/>
       <c r="F31" s="80"/>
       <c r="G31" s="80"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="147" t="s">
+      <c r="H31" s="150"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="149" t="s">
         <v>86</v>
       </c>
       <c r="K31" s="80"/>
-      <c r="L31" s="148"/>
+      <c r="L31" s="150"/>
       <c r="M31" s="104"/>
       <c r="N31" s="80"/>
       <c r="O31" s="80"/>
@@ -3156,7 +3160,7 @@
       <c r="Q31" s="99"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A32" s="149" t="s">
+      <c r="A32" s="151" t="s">
         <v>87</v>
       </c>
       <c r="B32" s="82"/>
